--- a/ch_09_text_analysis/ch_09_solutions.xlsx
+++ b/ch_09_text_analysis/ch_09_solutions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30021"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_09_text_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2345F755-787B-4640-9670-1323C675C294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2753BC59-FE1E-4911-BF98-59D25AD5F5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reviews" sheetId="1" r:id="rId1"/>
@@ -1364,10 +1364,10 @@
       <xdr:rowOff>110067</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>876299</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>162278</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>57133</xdr:rowOff>
+      <xdr:rowOff>57131</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1413,10 +1413,10 @@
       <xdr:rowOff>45262</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2002366</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1343378</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>147665</xdr:rowOff>
+      <xdr:rowOff>147663</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1462,10 +1462,10 @@
       <xdr:rowOff>118532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>526652</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>454685</xdr:colOff>
       <xdr:row>107</xdr:row>
-      <xdr:rowOff>48267</xdr:rowOff>
+      <xdr:rowOff>48265</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1512,7 +1512,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2624524</xdr:colOff>
+      <xdr:colOff>521970</xdr:colOff>
       <xdr:row>137</xdr:row>
       <xdr:rowOff>165101</xdr:rowOff>
     </xdr:to>
@@ -1560,10 +1560,10 @@
       <xdr:rowOff>139699</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>471607</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>298039</xdr:colOff>
       <xdr:row>166</xdr:row>
-      <xdr:rowOff>21174</xdr:rowOff>
+      <xdr:rowOff>21175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1609,8 +1609,8 @@
       <xdr:rowOff>46567</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1555046</xdr:colOff>
       <xdr:row>189</xdr:row>
       <xdr:rowOff>109421</xdr:rowOff>
     </xdr:to>
@@ -5974,8 +5974,8 @@
   <dimension ref="A1:D172"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="15.3515625" customWidth="1"/>
+    <col min="1" max="1" width="43.3515625" customWidth="1"/>
+    <col min="2" max="2" width="44.5859375" customWidth="1"/>
     <col min="4" max="4" width="46.5859375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5994,7 +5994,7 @@
         <v>review</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="86" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:4" ht="71.7" x14ac:dyDescent="0.5">
       <c r="A2" t="str">
         <v>Electronics</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>Wonderfull purchase. My neck pain from working at a laptop all day disappeared within a week of using this stand. The aluminum construction feels solid and the hinge holds any angle I set it to without drifting. Folds flat for travel.</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="71.7" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
       <c r="A3" t="str">
         <v>Clothing</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>The jacket is water resistant at best, not waterproof as advertised. During a steady rain I got damp underneath within about 20 minutes. Fine for a quick dash to the car but not for extended outdoor use.</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="71.7" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
       <c r="A4" t="str">
         <v>Home</v>
       </c>
@@ -6073,7 +6073,7 @@
         <v>review_clean</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="71.7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:4" ht="86" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="str">
         <v>Wonderfull purchase. My neck pain from working at a laptop all day disappeared within a week of using this stand. The aluminum construction feels solid and the hinge holds any angle I set it to without drifting. Folds flat for travel.</v>
       </c>
@@ -6081,7 +6081,7 @@
         <v>wonderfull purchase. my neck pain from working at a laptop all day disappeared within a week of using this stand. the aluminum construction feels solid and the hinge holds any angle i set it to without drifting. folds flat for travel.</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:4" ht="71.7" x14ac:dyDescent="0.5">
       <c r="A11" s="3" t="str">
         <v>The jacket is water resistant at best, not waterproof as advertised. During a steady rain I got damp underneath within about 20 minutes. Fine for a quick dash to the car but not for extended outdoor use.</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>the jacket is water resistant at best, not waterproof as advertised. during a steady rain i got damp underneath within about 20 minutes. fine for a quick dash to the car but not for extended outdoor use.</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:4" ht="71.7" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="str">
         <v>Lovely candle. The scent throw is good — I can smell it from the next room when it's been burning for a while. My only complaint is that the jar gets quite hot so I have to be careful where I place it.</v>
       </c>
@@ -6097,11 +6097,11 @@
         <v>lovely candle. the scent throw is good — i can smell it from the next room when it's been burning for a while. my only complaint is that the jar gets quite hot so i have to be careful where i place it.</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="143.35" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A14" s="3" t="str" cm="1">
         <f t="array" ref="A14:C19">_xlfn._xlws.PY(2,0)</f>
         <v>review_clean</v>
@@ -6113,7 +6113,7 @@
         <v>sentiment</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="71.7" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:4" ht="372.7" x14ac:dyDescent="0.5">
       <c r="A15" s="3" t="str">
         <v>wonderfull purchase. my neck pain from working at a laptop all day disappeared within a week of using this stand. the aluminum construction feels solid and the hinge holds any angle i set it to without drifting. folds flat for travel.</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>negative</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:4" ht="358.35" x14ac:dyDescent="0.5">
       <c r="A16" s="3" t="str">
         <v>the jacket is water resistant at best, not waterproof as advertised. during a steady rain i got damp underneath within about 20 minutes. fine for a quick dash to the car but not for extended outdoor use.</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>positive</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:3" ht="344" x14ac:dyDescent="0.5">
       <c r="A17" s="3" t="str">
         <v>lovely candle. the scent throw is good — i can smell it from the next room when it's been burning for a while. my only complaint is that the jar gets quite hot so i have to be careful where i place it.</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>positive</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="71.7" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:3" ht="372.7" x14ac:dyDescent="0.5">
       <c r="A18" s="3" t="str">
         <v>speical backpack. fits a ton of stuff for its size and the organization pockets are genuinely useful — i can find everything without digging. the laptop sleeve is padded enough to feel safe and the straps distribute weight evenly.</v>
       </c>
@@ -6157,7 +6157,7 @@
         <v>positive</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="43" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:3" ht="215" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="str">
         <v>comfortable on long hikes. i haven't had any hot spots or blisters. they do take a while to dry if they get fully wet though.</v>
       </c>

--- a/ch_09_text_analysis/ch_09_solutions.xlsx
+++ b/ch_09_text_analysis/ch_09_solutions.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30021"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30313"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_09_text_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_09_text_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2753BC59-FE1E-4911-BF98-59D25AD5F5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10000001_{853AA600-E78D-4F80-8891-FF9ECF63B8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reviews" sheetId="1" r:id="rId1"/>
     <sheet name="reviews_analysis" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -173,11 +174,17 @@
     </pythonScript>
     <pythonScript>
       <code>plt.figure(figsize=(8, 5))
-sns.countplot(data=reviews_df, x="sentiment",
-              order=["positive", "neutral", "negative"],
-              color="steelblue", edgecolor="black")
-plt.xlabel("Sentiment"); plt.ylabel("Number of Reviews")
-plt.title("Sentiment Distribution Across All Reviews")</code>
+sns.countplot(
+    data=reviews_df,
+    x="sentiment",
+    order=["positive", "neutral", "negative"],
+    color="steelblue",
+    edgecolor="black"
+)
+plt.xlabel("Sentiment", fontsize=11)
+plt.ylabel("Number of Reviews", fontsize=11)
+plt.title("Sentiment Distribution Across All Reviews", fontsize=13)
+plt.tick_params(labelsize=10)</code>
     </pythonScript>
     <pythonScript>
       <code>plt.figure(figsize=(8, 5))
@@ -219,11 +226,23 @@
 neg_top = pd.DataFrame(Counter(neg_words).most_common(15), columns=["word", "count"])</code>
     </pythonScript>
     <pythonScript>
-      <code>fig, axes = plt.subplots(1, 2, figsize=(14, 5))
-sns.barplot(data=pos_top, x="count", y="word", color="steelblue", ax=axes[0])
+      <code>fig, axes = plt.subplots(2, 1, figsize=(8, 10))
+sns.barplot(
+    data=pos_top,
+    x="count",
+    y="word",
+    color="steelblue",
+    ax=axes[0]
+)
 axes[0].set_title("Top Words in Positive Reviews")
 axes[0].set_xlabel("Count")
-sns.barplot(data=neg_top, x="count", y="word", color="coral", ax=axes[1])
+sns.barplot(
+    data=neg_top,
+    x="count",
+    y="word",
+    color="coral",
+    ax=axes[1]
+)
 axes[1].set_title("Top Words in Negative Reviews")
 axes[1].set_xlabel("Count")
 plt.tight_layout()</code>
@@ -1359,55 +1378,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>656167</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>110067</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>162278</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>57131</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Image generated by Python">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C52B044D-97CB-CA77-351A-599C31191BF7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="reviews_analysis!A27"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="656167" y="5207000"/>
-          <a:ext cx="2624666" cy="1767400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>711200</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>45262</xdr:rowOff>
@@ -1437,7 +1407,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1456,64 +1426,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>118532</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>454685</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>48265</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="Image generated by Python">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59914EEE-76B9-8456-8A0E-407CAB349028}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="reviews_analysis!A84"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="26877432"/>
-          <a:ext cx="12710185" cy="4480569"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>148167</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>144</xdr:row>
       <xdr:rowOff>177802</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>521970</xdr:colOff>
-      <xdr:row>137</xdr:row>
+      <xdr:row>158</xdr:row>
       <xdr:rowOff>165101</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1529,13 +1450,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="reviews_analysis!A125"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="reviews_analysis!A146"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1556,13 +1477,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>165</xdr:row>
       <xdr:rowOff>139699</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>298039</xdr:colOff>
-      <xdr:row>166</xdr:row>
+      <xdr:row>187</xdr:row>
       <xdr:rowOff>21175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1578,13 +1499,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="reviews_analysis!A146"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="reviews_analysis!A167"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1605,14 +1526,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>237067</xdr:colOff>
-      <xdr:row>174</xdr:row>
+      <xdr:row>195</xdr:row>
       <xdr:rowOff>46567</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1555046</xdr:colOff>
-      <xdr:row>189</xdr:row>
-      <xdr:rowOff>109421</xdr:rowOff>
+      <xdr:row>210</xdr:row>
+      <xdr:rowOff>109420</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1627,7 +1548,105 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="reviews_analysis!A172"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="reviews_analysis!A193"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="884767" y="41550167"/>
+          <a:ext cx="5168900" cy="2793354"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>111126</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>129930</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>103187</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7" descr="Image generated by Python">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE10CA20-0DDE-E722-7FAD-352CDB171B8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="reviews_analysis!A27"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="11691939"/>
+          <a:ext cx="3225555" cy="2182811"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>650874</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>179097</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Image generated by Python">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18D36EFC-0618-9B5A-3A31-A35B8555DFC2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="reviews_analysis!A84"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1640,8 +1659,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="884767" y="41550167"/>
-          <a:ext cx="5168900" cy="2793354"/>
+          <a:off x="0" y="22717125"/>
+          <a:ext cx="7580312" cy="9489785"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2173,15 +2192,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D270"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.1171875" customWidth="1"/>
-    <col min="2" max="2" width="24.52734375" customWidth="1"/>
+    <col min="1" max="1" width="20.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.53125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="62" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2195,7 +2214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2209,7 +2228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -2223,7 +2242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -2237,7 +2256,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2251,7 +2270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2265,7 +2284,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -2279,7 +2298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2293,7 +2312,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -2307,7 +2326,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -2321,7 +2340,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2335,7 +2354,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2349,7 +2368,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -2363,7 +2382,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2377,7 +2396,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -2391,7 +2410,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -2405,7 +2424,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -2419,7 +2438,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -2433,7 +2452,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -2447,7 +2466,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -2461,7 +2480,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2475,7 +2494,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -2489,7 +2508,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -2503,7 +2522,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -2517,7 +2536,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -2531,7 +2550,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -2545,7 +2564,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -2559,7 +2578,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -2573,7 +2592,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -2587,7 +2606,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -2601,7 +2620,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -2615,7 +2634,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -2629,7 +2648,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -2643,7 +2662,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -2657,7 +2676,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -2671,7 +2690,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -2685,7 +2704,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -2699,7 +2718,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -2713,7 +2732,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>20</v>
       </c>
@@ -2727,7 +2746,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -2741,7 +2760,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -2755,7 +2774,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -2769,7 +2788,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -2783,7 +2802,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -2797,7 +2816,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -2811,7 +2830,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>10</v>
       </c>
@@ -2825,7 +2844,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -2839,7 +2858,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -2853,7 +2872,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>20</v>
       </c>
@@ -2867,7 +2886,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -2881,7 +2900,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -2895,7 +2914,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -2909,7 +2928,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -2923,7 +2942,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>20</v>
       </c>
@@ -2937,7 +2956,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>10</v>
       </c>
@@ -2951,7 +2970,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -2965,7 +2984,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -2979,7 +2998,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -2993,7 +3012,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -3007,7 +3026,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -3021,7 +3040,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -3035,7 +3054,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -3049,7 +3068,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -3063,7 +3082,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>20</v>
       </c>
@@ -3077,7 +3096,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -3091,7 +3110,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>20</v>
       </c>
@@ -3105,7 +3124,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>20</v>
       </c>
@@ -3119,7 +3138,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>4</v>
       </c>
@@ -3133,7 +3152,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -3147,7 +3166,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -3161,7 +3180,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -3175,7 +3194,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -3189,7 +3208,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>10</v>
       </c>
@@ -3203,7 +3222,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>20</v>
       </c>
@@ -3217,7 +3236,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -3231,7 +3250,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>10</v>
       </c>
@@ -3245,7 +3264,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>10</v>
       </c>
@@ -3259,7 +3278,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>20</v>
       </c>
@@ -3273,7 +3292,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>10</v>
       </c>
@@ -3287,7 +3306,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>20</v>
       </c>
@@ -3301,7 +3320,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>20</v>
       </c>
@@ -3315,7 +3334,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -3329,7 +3348,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>10</v>
       </c>
@@ -3343,7 +3362,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>10</v>
       </c>
@@ -3357,7 +3376,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>10</v>
       </c>
@@ -3371,7 +3390,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>10</v>
       </c>
@@ -3385,7 +3404,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>7</v>
       </c>
@@ -3399,7 +3418,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>7</v>
       </c>
@@ -3413,7 +3432,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>10</v>
       </c>
@@ -3427,7 +3446,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>10</v>
       </c>
@@ -3441,7 +3460,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>7</v>
       </c>
@@ -3455,7 +3474,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>20</v>
       </c>
@@ -3469,7 +3488,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>10</v>
       </c>
@@ -3483,7 +3502,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>7</v>
       </c>
@@ -3497,7 +3516,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -3511,7 +3530,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -3525,7 +3544,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>20</v>
       </c>
@@ -3539,7 +3558,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>20</v>
       </c>
@@ -3553,7 +3572,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>4</v>
       </c>
@@ -3567,7 +3586,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>10</v>
       </c>
@@ -3581,7 +3600,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>20</v>
       </c>
@@ -3595,7 +3614,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>7</v>
       </c>
@@ -3609,7 +3628,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>7</v>
       </c>
@@ -3623,7 +3642,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>10</v>
       </c>
@@ -3637,7 +3656,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>7</v>
       </c>
@@ -3651,7 +3670,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>7</v>
       </c>
@@ -3665,7 +3684,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>10</v>
       </c>
@@ -3679,7 +3698,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>20</v>
       </c>
@@ -3693,7 +3712,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>10</v>
       </c>
@@ -3707,7 +3726,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>7</v>
       </c>
@@ -3721,7 +3740,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>4</v>
       </c>
@@ -3735,7 +3754,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>4</v>
       </c>
@@ -3749,7 +3768,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>4</v>
       </c>
@@ -3763,7 +3782,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>20</v>
       </c>
@@ -3777,7 +3796,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>20</v>
       </c>
@@ -3791,7 +3810,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>7</v>
       </c>
@@ -3805,7 +3824,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>4</v>
       </c>
@@ -3819,7 +3838,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>20</v>
       </c>
@@ -3833,7 +3852,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>7</v>
       </c>
@@ -3847,7 +3866,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>10</v>
       </c>
@@ -3861,7 +3880,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>10</v>
       </c>
@@ -3875,7 +3894,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>20</v>
       </c>
@@ -3889,7 +3908,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>10</v>
       </c>
@@ -3903,7 +3922,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>10</v>
       </c>
@@ -3917,7 +3936,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>7</v>
       </c>
@@ -3931,7 +3950,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>10</v>
       </c>
@@ -3945,7 +3964,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>4</v>
       </c>
@@ -3959,7 +3978,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>4</v>
       </c>
@@ -3973,7 +3992,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>4</v>
       </c>
@@ -3987,7 +4006,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>4</v>
       </c>
@@ -4001,7 +4020,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -4015,7 +4034,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>7</v>
       </c>
@@ -4029,7 +4048,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>20</v>
       </c>
@@ -4043,7 +4062,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>10</v>
       </c>
@@ -4057,7 +4076,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>4</v>
       </c>
@@ -4071,7 +4090,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>20</v>
       </c>
@@ -4085,7 +4104,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>20</v>
       </c>
@@ -4099,7 +4118,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -4113,7 +4132,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>20</v>
       </c>
@@ -4127,7 +4146,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>7</v>
       </c>
@@ -4141,7 +4160,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>4</v>
       </c>
@@ -4155,7 +4174,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>7</v>
       </c>
@@ -4169,7 +4188,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -4183,7 +4202,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="71.7" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>4</v>
       </c>
@@ -4197,7 +4216,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>20</v>
       </c>
@@ -4211,7 +4230,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>10</v>
       </c>
@@ -4225,7 +4244,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>4</v>
       </c>
@@ -4239,7 +4258,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>7</v>
       </c>
@@ -4253,7 +4272,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>10</v>
       </c>
@@ -4267,7 +4286,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>4</v>
       </c>
@@ -4281,7 +4300,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>20</v>
       </c>
@@ -4295,7 +4314,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>10</v>
       </c>
@@ -4309,7 +4328,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>20</v>
       </c>
@@ -4323,7 +4342,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>4</v>
       </c>
@@ -4337,7 +4356,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>7</v>
       </c>
@@ -4351,7 +4370,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>20</v>
       </c>
@@ -4365,7 +4384,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>4</v>
       </c>
@@ -4379,7 +4398,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>4</v>
       </c>
@@ -4393,7 +4412,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>4</v>
       </c>
@@ -4407,7 +4426,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>7</v>
       </c>
@@ -4421,7 +4440,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -4435,7 +4454,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>4</v>
       </c>
@@ -4449,7 +4468,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>4</v>
       </c>
@@ -4463,7 +4482,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>7</v>
       </c>
@@ -4477,7 +4496,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>20</v>
       </c>
@@ -4491,7 +4510,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>7</v>
       </c>
@@ -4505,7 +4524,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>7</v>
       </c>
@@ -4519,7 +4538,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -4533,7 +4552,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>4</v>
       </c>
@@ -4547,7 +4566,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>20</v>
       </c>
@@ -4561,7 +4580,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>4</v>
       </c>
@@ -4575,7 +4594,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>20</v>
       </c>
@@ -4589,7 +4608,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>20</v>
       </c>
@@ -4603,7 +4622,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>10</v>
       </c>
@@ -4617,7 +4636,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>7</v>
       </c>
@@ -4631,7 +4650,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>20</v>
       </c>
@@ -4645,7 +4664,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>7</v>
       </c>
@@ -4659,7 +4678,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>4</v>
       </c>
@@ -4673,7 +4692,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>4</v>
       </c>
@@ -4687,7 +4706,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>4</v>
       </c>
@@ -4701,7 +4720,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>4</v>
       </c>
@@ -4715,7 +4734,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>10</v>
       </c>
@@ -4729,7 +4748,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>20</v>
       </c>
@@ -4743,7 +4762,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>20</v>
       </c>
@@ -4757,7 +4776,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>20</v>
       </c>
@@ -4771,7 +4790,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>10</v>
       </c>
@@ -4785,7 +4804,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>4</v>
       </c>
@@ -4799,7 +4818,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>7</v>
       </c>
@@ -4813,7 +4832,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>20</v>
       </c>
@@ -4827,7 +4846,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>4</v>
       </c>
@@ -4841,7 +4860,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>4</v>
       </c>
@@ -4855,7 +4874,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>4</v>
       </c>
@@ -4869,7 +4888,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>7</v>
       </c>
@@ -4883,7 +4902,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>20</v>
       </c>
@@ -4897,7 +4916,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>7</v>
       </c>
@@ -4911,7 +4930,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>7</v>
       </c>
@@ -4925,7 +4944,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>4</v>
       </c>
@@ -4939,7 +4958,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>10</v>
       </c>
@@ -4953,7 +4972,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>20</v>
       </c>
@@ -4967,7 +4986,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>4</v>
       </c>
@@ -4981,7 +5000,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>10</v>
       </c>
@@ -4995,7 +5014,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="202" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>4</v>
       </c>
@@ -5009,7 +5028,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="203" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>20</v>
       </c>
@@ -5023,7 +5042,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>4</v>
       </c>
@@ -5037,7 +5056,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="205" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>20</v>
       </c>
@@ -5051,7 +5070,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="206" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>4</v>
       </c>
@@ -5065,7 +5084,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>20</v>
       </c>
@@ -5079,7 +5098,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>7</v>
       </c>
@@ -5093,7 +5112,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>10</v>
       </c>
@@ -5107,7 +5126,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="210" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>10</v>
       </c>
@@ -5121,7 +5140,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>10</v>
       </c>
@@ -5135,7 +5154,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>7</v>
       </c>
@@ -5149,7 +5168,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>10</v>
       </c>
@@ -5163,7 +5182,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="214" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>4</v>
       </c>
@@ -5177,7 +5196,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="215" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>4</v>
       </c>
@@ -5191,7 +5210,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="216" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>20</v>
       </c>
@@ -5205,7 +5224,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="217" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>10</v>
       </c>
@@ -5219,7 +5238,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="218" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>7</v>
       </c>
@@ -5233,7 +5252,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="219" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>4</v>
       </c>
@@ -5247,7 +5266,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="220" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>4</v>
       </c>
@@ -5261,7 +5280,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>10</v>
       </c>
@@ -5275,7 +5294,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>10</v>
       </c>
@@ -5289,7 +5308,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>7</v>
       </c>
@@ -5303,7 +5322,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>20</v>
       </c>
@@ -5317,7 +5336,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>7</v>
       </c>
@@ -5331,7 +5350,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>20</v>
       </c>
@@ -5345,7 +5364,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>20</v>
       </c>
@@ -5359,7 +5378,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>7</v>
       </c>
@@ -5373,7 +5392,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>20</v>
       </c>
@@ -5387,7 +5406,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="230" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>20</v>
       </c>
@@ -5401,7 +5420,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="231" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>20</v>
       </c>
@@ -5415,7 +5434,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="232" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>20</v>
       </c>
@@ -5429,7 +5448,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="233" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>7</v>
       </c>
@@ -5443,7 +5462,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="234" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>4</v>
       </c>
@@ -5457,7 +5476,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="235" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>4</v>
       </c>
@@ -5471,7 +5490,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="236" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>10</v>
       </c>
@@ -5485,7 +5504,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="237" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>20</v>
       </c>
@@ -5499,7 +5518,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="238" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>4</v>
       </c>
@@ -5513,7 +5532,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="239" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>20</v>
       </c>
@@ -5527,7 +5546,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="240" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>20</v>
       </c>
@@ -5541,7 +5560,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="241" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>20</v>
       </c>
@@ -5555,7 +5574,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="242" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>10</v>
       </c>
@@ -5569,7 +5588,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="243" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>7</v>
       </c>
@@ -5583,7 +5602,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="244" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>4</v>
       </c>
@@ -5597,7 +5616,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="245" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>20</v>
       </c>
@@ -5611,7 +5630,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="246" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>4</v>
       </c>
@@ -5625,7 +5644,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>10</v>
       </c>
@@ -5639,7 +5658,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="248" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>7</v>
       </c>
@@ -5653,7 +5672,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="249" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>7</v>
       </c>
@@ -5667,7 +5686,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="250" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>7</v>
       </c>
@@ -5681,7 +5700,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="251" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>7</v>
       </c>
@@ -5695,7 +5714,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>4</v>
       </c>
@@ -5709,7 +5728,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>7</v>
       </c>
@@ -5723,7 +5742,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="254" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>10</v>
       </c>
@@ -5737,7 +5756,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="255" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>7</v>
       </c>
@@ -5751,7 +5770,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="256" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>4</v>
       </c>
@@ -5765,7 +5784,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="257" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>20</v>
       </c>
@@ -5779,7 +5798,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>10</v>
       </c>
@@ -5793,7 +5812,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="259" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>7</v>
       </c>
@@ -5807,7 +5826,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>7</v>
       </c>
@@ -5821,7 +5840,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="261" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>10</v>
       </c>
@@ -5835,7 +5854,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="262" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>10</v>
       </c>
@@ -5849,7 +5868,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>4</v>
       </c>
@@ -5863,7 +5882,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="264" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>7</v>
       </c>
@@ -5877,7 +5896,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="265" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>7</v>
       </c>
@@ -5891,7 +5910,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="266" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>4</v>
       </c>
@@ -5905,7 +5924,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="267" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>7</v>
       </c>
@@ -5919,7 +5938,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="268" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>10</v>
       </c>
@@ -5933,7 +5952,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="269" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>7</v>
       </c>
@@ -5947,7 +5966,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="270" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>10</v>
       </c>
@@ -5971,15 +5990,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822C8D37-C826-49AC-8AE8-254FD48FF68A}">
-  <dimension ref="A1:D172"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:D193"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="43.3515625" customWidth="1"/>
-    <col min="2" max="2" width="44.5859375" customWidth="1"/>
-    <col min="4" max="4" width="46.5859375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="43.33203125" customWidth="1"/>
+    <col min="2" max="2" width="44.59765625" customWidth="1"/>
+    <col min="4" max="4" width="46.59765625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="str" cm="1">
         <f t="array" ref="A1:D6">_xlfn._xlws.PY(0,0,reviews[#All])</f>
         <v>product_category</v>
@@ -5994,7 +6013,7 @@
         <v>review</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="71.7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A2" t="str">
         <v>Electronics</v>
       </c>
@@ -6008,7 +6027,7 @@
         <v>Wonderfull purchase. My neck pain from working at a laptop all day disappeared within a week of using this stand. The aluminum construction feels solid and the hinge holds any angle I set it to without drifting. Folds flat for travel.</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A3" t="str">
         <v>Clothing</v>
       </c>
@@ -6022,7 +6041,7 @@
         <v>The jacket is water resistant at best, not waterproof as advertised. During a steady rain I got damp underneath within about 20 minutes. Fine for a quick dash to the car but not for extended outdoor use.</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="57.35" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A4" t="str">
         <v>Home</v>
       </c>
@@ -6036,7 +6055,7 @@
         <v>Lovely candle. The scent throw is good — I can smell it from the next room when it's been burning for a while. My only complaint is that the jar gets quite hot so I have to be careful where I place it.</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="71.7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A5" t="str">
         <v>Clothing</v>
       </c>
@@ -6050,7 +6069,7 @@
         <v>Speical backpack. Fits a ton of stuff for its size and the organization pockets are genuinely useful — I can find everything without digging. The laptop sleeve is padded enough to feel safe and the straps distribute weight evenly.</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="43" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A6" t="str">
         <v>Clothing</v>
       </c>
@@ -6064,7 +6083,7 @@
         <v>Comfortable on long hikes. I haven't had any hot spots or blisters. They do take a while to dry if they get fully wet though.</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="str" cm="1">
         <f t="array" ref="A9:B12">_xlfn._xlws.PY(1,0)</f>
         <v>review</v>
@@ -6073,7 +6092,7 @@
         <v>review_clean</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="86" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="str">
         <v>Wonderfull purchase. My neck pain from working at a laptop all day disappeared within a week of using this stand. The aluminum construction feels solid and the hinge holds any angle I set it to without drifting. Folds flat for travel.</v>
       </c>
@@ -6081,7 +6100,7 @@
         <v>wonderfull purchase. my neck pain from working at a laptop all day disappeared within a week of using this stand. the aluminum construction feels solid and the hinge holds any angle i set it to without drifting. folds flat for travel.</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="71.7" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="str">
         <v>The jacket is water resistant at best, not waterproof as advertised. During a steady rain I got damp underneath within about 20 minutes. Fine for a quick dash to the car but not for extended outdoor use.</v>
       </c>
@@ -6089,7 +6108,7 @@
         <v>the jacket is water resistant at best, not waterproof as advertised. during a steady rain i got damp underneath within about 20 minutes. fine for a quick dash to the car but not for extended outdoor use.</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="71.7" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="str">
         <v>Lovely candle. The scent throw is good — I can smell it from the next room when it's been burning for a while. My only complaint is that the jar gets quite hot so I have to be careful where I place it.</v>
       </c>
@@ -6097,11 +6116,11 @@
         <v>lovely candle. the scent throw is good — i can smell it from the next room when it's been burning for a while. my only complaint is that the jar gets quite hot so i have to be careful where i place it.</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:4" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="str" cm="1">
         <f t="array" ref="A14:C19">_xlfn._xlws.PY(2,0)</f>
         <v>review_clean</v>
@@ -6113,7 +6132,7 @@
         <v>sentiment</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="372.7" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="str">
         <v>wonderfull purchase. my neck pain from working at a laptop all day disappeared within a week of using this stand. the aluminum construction feels solid and the hinge holds any angle i set it to without drifting. folds flat for travel.</v>
       </c>
@@ -6124,7 +6143,7 @@
         <v>negative</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="358.35" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="str">
         <v>the jacket is water resistant at best, not waterproof as advertised. during a steady rain i got damp underneath within about 20 minutes. fine for a quick dash to the car but not for extended outdoor use.</v>
       </c>
@@ -6135,7 +6154,7 @@
         <v>positive</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="344" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="str">
         <v>lovely candle. the scent throw is good — i can smell it from the next room when it's been burning for a while. my only complaint is that the jar gets quite hot so i have to be careful where i place it.</v>
       </c>
@@ -6146,7 +6165,7 @@
         <v>positive</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="372.7" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="str">
         <v>speical backpack. fits a ton of stuff for its size and the organization pockets are genuinely useful — i can find everything without digging. the laptop sleeve is padded enough to feel safe and the straps distribute weight evenly.</v>
       </c>
@@ -6157,7 +6176,7 @@
         <v>positive</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="215" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="str">
         <v>comfortable on long hikes. i haven't had any hot spots or blisters. they do take a while to dry if they get fully wet though.</v>
       </c>
@@ -6168,75 +6187,75 @@
         <v>positive</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="e" cm="1" vm="1">
         <f t="array" ref="A27">_xlfn._xlws.PY(3,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" t="e" cm="1" vm="2">
         <f t="array" ref="A39">_xlfn._xlws.PY(4,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A55" t="str" cm="1">
         <f t="array" ref="A55:A65">_xlfn._xlws.PY(5,0)</f>
         <v>tokens</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A56" t="str">
         <v>wonderfull</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A57" t="str">
         <v>purchase</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A58" t="str">
         <v>neck</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A59" t="str">
         <v>pain</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A60" t="str">
         <v>working</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A61" t="str">
         <v>laptop</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A62" t="str">
         <v>day</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A63" t="str">
         <v>disappeared</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A64" t="str">
         <v>within</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A65" t="str">
         <v>week</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A68" t="str" cm="1">
         <f t="array" ref="A68:B78">_xlfn._xlws.PY(6,0)</f>
         <v>word</v>
@@ -6245,7 +6264,7 @@
         <v>count</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A69" t="str">
         <v>good</v>
       </c>
@@ -6253,7 +6272,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A70" t="str">
         <v>works</v>
       </c>
@@ -6261,7 +6280,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A71" t="str">
         <v>enough</v>
       </c>
@@ -6269,7 +6288,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A72" t="str">
         <v>without</v>
       </c>
@@ -6277,7 +6296,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A73" t="str">
         <v>fine</v>
       </c>
@@ -6285,7 +6304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A74" t="str">
         <v>great</v>
       </c>
@@ -6293,7 +6312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A75" t="str">
         <v>use</v>
       </c>
@@ -6301,7 +6320,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A76" t="str">
         <v>expected</v>
       </c>
@@ -6309,7 +6328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A77" t="str">
         <v>warm</v>
       </c>
@@ -6317,7 +6336,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A78" t="str">
         <v>one</v>
       </c>
@@ -6325,155 +6344,155 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A80" t="e" cm="1" vm="3">
         <f t="array" ref="A80">_xlfn._xlws.PY(7,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A84" t="e" cm="1" vm="4">
         <f t="array" ref="A84">_xlfn._xlws.PY(8,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A112" t="str" cm="1">
-        <f t="array" ref="A112:C122">_xlfn._xlws.PY(9,0)</f>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A133" t="str" cm="1">
+        <f t="array" ref="A133:C143">_xlfn._xlws.PY(9,0)</f>
         <v/>
       </c>
-      <c r="B112" t="str">
+      <c r="B133" t="str">
         <v>term</v>
       </c>
-      <c r="C112" s="5" t="str">
+      <c r="C133" s="5" t="str">
         <v>tfidf_score</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A113">
-        <v>7</v>
-      </c>
-      <c r="B113" t="str">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A134">
+        <v>7</v>
+      </c>
+      <c r="B134" t="str">
         <v>use</v>
       </c>
-      <c r="C113" s="5">
+      <c r="C134" s="5">
         <v>0.1342965108401537</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A114">
-        <v>4</v>
-      </c>
-      <c r="B114" t="str">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A135">
+        <v>4</v>
+      </c>
+      <c r="B135" t="str">
         <v>good</v>
       </c>
-      <c r="C114" s="5">
+      <c r="C135" s="5">
         <v>0.12112288412711421</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A115">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A136">
         <v>8</v>
       </c>
-      <c r="B115" t="str">
+      <c r="B136" t="str">
         <v>ve</v>
       </c>
-      <c r="C115" s="5">
+      <c r="C136" s="5">
         <v>9.3458794007170262E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A116">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A137">
         <v>1</v>
       </c>
-      <c r="B116" t="str">
+      <c r="B137" t="str">
         <v>expected</v>
       </c>
-      <c r="C116" s="5">
+      <c r="C137" s="5">
         <v>8.591450104638905E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A117">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A138">
         <v>2</v>
       </c>
-      <c r="B117" t="str">
+      <c r="B138" t="str">
         <v>fine</v>
       </c>
-      <c r="C117" s="5">
+      <c r="C138" s="5">
         <v>8.4462865623648603E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A118">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A139">
         <v>9</v>
       </c>
-      <c r="B118" t="str">
+      <c r="B139" t="str">
         <v>works</v>
       </c>
-      <c r="C118" s="5">
+      <c r="C139" s="5">
         <v>8.2781363122761048E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A119">
-        <v>5</v>
-      </c>
-      <c r="B119" t="str">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A140">
+        <v>5</v>
+      </c>
+      <c r="B140" t="str">
         <v>great</v>
       </c>
-      <c r="C119" s="5">
+      <c r="C140" s="5">
         <v>7.2733192664300075E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A120">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A141">
         <v>0</v>
       </c>
-      <c r="B120" t="str">
+      <c r="B141" t="str">
         <v>doesn</v>
       </c>
-      <c r="C120" s="5">
+      <c r="C141" s="5">
         <v>6.0310046552266523E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A121">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A142">
         <v>6</v>
       </c>
-      <c r="B121" t="str">
+      <c r="B142" t="str">
         <v>quality</v>
       </c>
-      <c r="C121" s="5">
+      <c r="C142" s="5">
         <v>5.7756006347849144E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A122">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A143">
         <v>3</v>
       </c>
-      <c r="B122" t="str">
+      <c r="B143" t="str">
         <v>fit</v>
       </c>
-      <c r="C122" s="5">
+      <c r="C143" s="5">
         <v>5.5274745427059707E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A125" t="e" cm="1" vm="5">
-        <f t="array" ref="A125">_xlfn._xlws.PY(10,0)</f>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A146" t="e" cm="1" vm="5">
+        <f t="array" ref="A146">_xlfn._xlws.PY(10,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A146" t="e" cm="1" vm="6">
-        <f t="array" ref="A146">_xlfn._xlws.PY(11,0)</f>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A167" t="e" cm="1" vm="6">
+        <f t="array" ref="A167">_xlfn._xlws.PY(11,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A172" t="e" cm="1" vm="7">
-        <f t="array" ref="A172">_xlfn._xlws.PY(12,0)</f>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A193" t="e" cm="1" vm="7">
+        <f t="array" ref="A193">_xlfn._xlws.PY(12,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>

--- a/ch_09_text_analysis/ch_09_solutions.xlsx
+++ b/ch_09_text_analysis/ch_09_solutions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_09_text_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10000001_{853AA600-E78D-4F80-8891-FF9ECF63B8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26C8C93-FB49-44B2-B745-DD3D0D488FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="reviews_analysis" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -134,7 +133,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization userModified="1">
+    <initialization>
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -163,14 +162,14 @@
       <code>from nltk.sentiment.vader import SentimentIntensityAnalyzer
 sid = SentimentIntensityAnalyzer()
 # Score each review and extract compound sentiment
-scores = reviews_df["review_clean"].apply(sid.polarity_scores)
+scores = reviews_df["review"].apply(sid.polarity_scores)
 reviews_df["compound"] = scores.apply(lambda x: x["compound"])
 # Classify sentiment
 reviews_df["sentiment"] = "neutral"
 reviews_df.loc[reviews_df["compound"] &gt;= 0.05, "sentiment"] = "positive"
 reviews_df.loc[reviews_df["compound"] &lt;= -0.05, "sentiment"] = "negative"
 # Preview results
-reviews_df[["review_clean", "compound", "sentiment"]].head()</code>
+reviews_df[["review", "compound", "sentiment"]].head()</code>
     </pythonScript>
     <pythonScript>
       <code>plt.figure(figsize=(8, 5))
@@ -1383,8 +1382,8 @@
       <xdr:rowOff>45262</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1343378</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>517878</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>147663</xdr:rowOff>
     </xdr:to>
@@ -1433,7 +1432,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>521970</xdr:colOff>
+      <xdr:colOff>2879408</xdr:colOff>
       <xdr:row>158</xdr:row>
       <xdr:rowOff>165101</xdr:rowOff>
     </xdr:to>
@@ -1481,8 +1480,8 @@
       <xdr:rowOff>139699</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>298039</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>51976</xdr:colOff>
       <xdr:row>187</xdr:row>
       <xdr:rowOff>21175</xdr:rowOff>
     </xdr:to>
@@ -1530,8 +1529,8 @@
       <xdr:rowOff>46567</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1555046</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>586671</xdr:colOff>
       <xdr:row>210</xdr:row>
       <xdr:rowOff>109420</xdr:rowOff>
     </xdr:to>
@@ -1629,7 +1628,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>650874</xdr:colOff>
+      <xdr:colOff>3008312</xdr:colOff>
       <xdr:row>134</xdr:row>
       <xdr:rowOff>179097</xdr:rowOff>
     </xdr:to>
@@ -5994,7 +5993,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="43.33203125" customWidth="1"/>
-    <col min="2" max="2" width="44.59765625" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" customWidth="1"/>
     <col min="4" max="4" width="46.59765625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6123,7 +6122,7 @@
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="str" cm="1">
         <f t="array" ref="A14:C19">_xlfn._xlws.PY(2,0)</f>
-        <v>review_clean</v>
+        <v>review</v>
       </c>
       <c r="B14" t="str">
         <v>compound</v>
@@ -6134,7 +6133,7 @@
     </row>
     <row r="15" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="str">
-        <v>wonderfull purchase. my neck pain from working at a laptop all day disappeared within a week of using this stand. the aluminum construction feels solid and the hinge holds any angle i set it to without drifting. folds flat for travel.</v>
+        <v>Wonderfull purchase. My neck pain from working at a laptop all day disappeared within a week of using this stand. The aluminum construction feels solid and the hinge holds any angle I set it to without drifting. Folds flat for travel.</v>
       </c>
       <c r="B15" s="4">
         <v>-0.55740000000000001</v>
@@ -6145,7 +6144,7 @@
     </row>
     <row r="16" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="str">
-        <v>the jacket is water resistant at best, not waterproof as advertised. during a steady rain i got damp underneath within about 20 minutes. fine for a quick dash to the car but not for extended outdoor use.</v>
+        <v>The jacket is water resistant at best, not waterproof as advertised. During a steady rain I got damp underneath within about 20 minutes. Fine for a quick dash to the car but not for extended outdoor use.</v>
       </c>
       <c r="B16" s="4">
         <v>0.45879999999999999</v>
@@ -6156,7 +6155,7 @@
     </row>
     <row r="17" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="str">
-        <v>lovely candle. the scent throw is good — i can smell it from the next room when it's been burning for a while. my only complaint is that the jar gets quite hot so i have to be careful where i place it.</v>
+        <v>Lovely candle. The scent throw is good — I can smell it from the next room when it's been burning for a while. My only complaint is that the jar gets quite hot so I have to be careful where I place it.</v>
       </c>
       <c r="B17" s="4">
         <v>0.72689999999999999</v>
@@ -6167,7 +6166,7 @@
     </row>
     <row r="18" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="str">
-        <v>speical backpack. fits a ton of stuff for its size and the organization pockets are genuinely useful — i can find everything without digging. the laptop sleeve is padded enough to feel safe and the straps distribute weight evenly.</v>
+        <v>Speical backpack. Fits a ton of stuff for its size and the organization pockets are genuinely useful — I can find everything without digging. The laptop sleeve is padded enough to feel safe and the straps distribute weight evenly.</v>
       </c>
       <c r="B18" s="4">
         <v>0.70030000000000003</v>
@@ -6178,7 +6177,7 @@
     </row>
     <row r="19" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="str">
-        <v>comfortable on long hikes. i haven't had any hot spots or blisters. they do take a while to dry if they get fully wet though.</v>
+        <v>Comfortable on long hikes. I haven't had any hot spots or blisters. They do take a while to dry if they get fully wet though.</v>
       </c>
       <c r="B19" s="4">
         <v>0.51060000000000005</v>
